--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/jun-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/jun-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>196849.9904</v>
+        <v>196849.99</v>
       </c>
     </row>
     <row r="7">
@@ -884,7 +884,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3213-113-CM26</t>
+          <t>4928-25-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -904,32 +904,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Enviada a Proveedor</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.180.500-k</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1604.12</v>
+        <v>1690.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3863-185-CM26</t>
+          <t>1388961-384-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -970,27 +970,27 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>65.118.035-K</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>ASOCIACION DE MUNICIPALIDADES PARA LA SEGURIDAD CIUDADANA EN LA ZONA ORIENTE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1000,13 +1000,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>7819.29</v>
+        <v>44627.86</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3678-177-CM26</t>
+          <t>3863-185-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1026,32 +1026,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.050.500-2</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PETORCA</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>14608.44</v>
+        <v>7819.29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4928-25-CM26</t>
+          <t>3678-177-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1087,32 +1087,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.050.500-2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE PETORCA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1122,13 +1122,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1690.75</v>
+        <v>14608.44</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1388961-384-CM26</t>
+          <t>4083-257-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1143,37 +1143,37 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>65.118.035-K</t>
+          <t>69.151.002-6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPALIDADES PARA LA SEGURIDAD CIUDADANA EN LA ZONA ORIENTE</t>
+          <t>I MUNICIPALIDAD DE CABRERO DEPARTAMENTO DE SALUD</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1183,13 +1183,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>44627.86</v>
+        <v>5247.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4083-257-CM26</t>
+          <t>894778-29-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1204,37 +1204,37 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.151.002-6</t>
+          <t>60.501.000-8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO DEPARTAMENTO DE SALUD</t>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>5247.9</v>
+        <v>41174.95</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>894778-29-CM26</t>
+          <t>4179-622-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1275,27 +1275,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.501.000-8</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL INTERIOR</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1305,13 +1305,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>41174.95</v>
+        <v>6424.57</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4179-622-CM26</t>
+          <t>3882-209-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1336,27 +1336,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>69.060.400-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1366,13 +1366,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>6424.57</v>
+        <v>17740.52</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3882-209-CM26</t>
+          <t>4022-302-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1392,22 +1392,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.060.400-0</t>
+          <t>69.250.800-9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
+          <t>Ilustre Municipalidad de Putre</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>17740.52</v>
+        <v>16382.49</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4022-302-CM26</t>
+          <t>4322-332-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1458,27 +1458,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.250.800-9</t>
+          <t>69.190.300-1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Putre</t>
+          <t>I MUNICIPALIDAD DE PERQUENCO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1488,13 +1488,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>16382.49</v>
+        <v>845.28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4322-332-CM26</t>
+          <t>527481-51-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1519,27 +1519,27 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.190.300-1</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERQUENCO</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>845.28</v>
+        <v>13305.39</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>527481-51-CM26</t>
+          <t>1973-1484-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1570,27 +1570,27 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>61.953.200-7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>CENTRO DE REFERENCIA DE SALUD DE PENALOLEN CORDILLERA ORIENTE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>13305.39</v>
+        <v>38738.67</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1973-1484-CM26</t>
+          <t>3553-199-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.953.200-7</t>
+          <t>61.402.000-8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>CENTRO DE REFERENCIA DE SALUD DE PENALOLEN CORDILLERA ORIENTE</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>38738.67</v>
+        <v>5158.29</v>
       </c>
     </row>
     <row r="21">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>104758.7345</v>
+        <v>104758.73</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3553-199-CM26</t>
+          <t>3515-294-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1757,111 +1757,50 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.402.000-8</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>5158.29</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>3515-294-CM26</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>jun-2026</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>69.060.300-4</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>CLOUDLATAM SPA</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>76.981.642-9</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="n">
         <v>150600.45</v>
       </c>
     </row>
